--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -753,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -799,7 +661,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -845,7 +707,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-18</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -891,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -937,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -983,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1029,7 +891,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1075,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1121,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1167,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1213,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1259,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1355,7 +1217,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1401,7 +1263,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1447,7 +1309,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1493,7 +1355,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1539,7 +1401,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1585,7 +1447,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1631,7 +1493,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1677,7 +1539,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1773,7 +1635,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1819,7 +1681,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1865,7 +1727,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1911,7 +1773,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1957,7 +1819,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-09-25</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2003,7 +1865,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2049,7 +1911,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-19</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2095,7 +1957,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-19</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2141,7 +2003,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2187,7 +2049,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2233,7 +2095,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2329,7 +2191,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2375,7 +2237,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-18</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2421,7 +2283,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2467,7 +2329,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2513,7 +2375,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-26</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2559,7 +2421,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2605,7 +2467,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2651,7 +2513,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-30</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2747,7 +2609,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2793,7 +2655,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2839,7 +2701,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2885,7 +2747,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2931,7 +2793,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2977,7 +2839,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3023,7 +2885,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3069,7 +2931,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-05</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3165,7 +3027,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3261,7 +3123,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3307,7 +3169,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3353,7 +3215,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3449,7 +3311,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-29</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3545,7 +3407,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3591,7 +3453,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3829,7 +3691,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3875,7 +3737,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3921,7 +3783,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3967,7 +3829,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-15</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4013,7 +3875,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4059,7 +3921,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4105,7 +3967,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4151,7 +4013,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4247,7 +4109,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4293,7 +4155,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4339,7 +4201,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4385,7 +4247,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4431,7 +4293,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4477,7 +4339,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4523,7 +4385,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4569,7 +4431,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4615,7 +4477,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4661,7 +4523,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4707,7 +4569,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4753,7 +4615,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4799,7 +4661,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4845,7 +4707,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4941,7 +4803,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-14</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4987,7 +4849,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-14</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5033,7 +4895,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5079,7 +4941,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5125,7 +4987,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-08-27</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5171,7 +5033,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5217,7 +5079,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-02</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5263,7 +5125,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5309,7 +5171,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5355,7 +5217,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-27</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5401,7 +5263,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5497,7 +5359,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5543,7 +5405,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5589,7 +5451,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5635,7 +5497,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5681,7 +5543,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-07</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5777,7 +5639,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5823,7 +5685,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5919,7 +5781,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5965,7 +5827,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6011,7 +5873,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6057,7 +5919,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6103,7 +5965,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6149,7 +6011,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6195,7 +6057,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6241,7 +6103,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6287,7 +6149,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-09</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6471,7 +6333,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6517,7 +6379,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6563,7 +6425,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6609,7 +6471,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6655,7 +6517,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6701,7 +6563,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6747,7 +6609,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6793,7 +6655,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6839,7 +6701,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6885,7 +6747,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6931,7 +6793,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6977,7 +6839,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7023,7 +6885,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7069,7 +6931,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7115,7 +6977,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7161,7 +7023,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7207,7 +7069,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7253,7 +7115,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7299,7 +7161,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7345,7 +7207,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7391,7 +7253,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7437,7 +7299,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7483,7 +7345,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7529,7 +7391,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7575,7 +7437,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7621,7 +7483,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7667,7 +7529,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7759,7 +7621,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7805,7 +7667,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7851,7 +7713,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7897,7 +7759,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-11</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7943,7 +7805,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7989,7 +7851,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8035,7 +7897,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8081,7 +7943,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8177,7 +8039,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8223,7 +8085,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8269,7 +8131,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8315,7 +8177,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8361,7 +8223,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8407,7 +8269,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8453,7 +8315,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8499,7 +8361,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8545,7 +8407,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8591,7 +8453,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8637,7 +8499,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8683,7 +8545,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8729,7 +8591,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8775,7 +8637,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8797,2180 +8659,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>St. George's Mansions - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>58 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>52 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3330呎 (4+房)
-$23,800万
-$71,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,674万
-$37,036/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 3330呎 (4+房)
-$21,380万
-$64,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,620万
-$36,288/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2141呎 (4+房)
-$12,168万
-$56,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1842呎 (3房)
-$9,512万
-$51,640/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-$2,544万
-$33,300/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 2141呎 (4+房)
-$12,018万
-$56,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1725呎 (3房)
-$9,210万
-$53,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,705万
-$37,465/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,900万
-$55,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,800万
-$51,044/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,466万
-$34,157/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 2024呎 (4+房)
-$11,800万
-$58,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,600万
-$49,884/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,700万
-$54,673/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,500万
-$49,304/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,382万
-$32,992/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,500万
-$53,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1841呎 (3房)
-$9,000万
-$48,886/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,340万
-$32,410/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,500万
-$53,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,380万
-$48,608/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,300万
-$52,804/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,280万
-$48,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,463万
-$34,111/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$11,000万
-$51,402/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1841呎 (3房)
-$8,900万
-$48,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,510万
-$34,765/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$10,500万
-$49,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,274万
-$47,993/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,222万
-$30,776/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$10,280万
-$48,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$7,950万
-$46,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$10,270万
-$47,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$7,838万
-$45,464/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,178万
-$30,169/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$10,450万
-$48,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1841呎 (3房)
-$8,600万
-$46,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,150万
-$29,778/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 2140呎 (4+房)
-$9,780万
-$45,701/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1841呎 (3房)
-$8,020万
-$43,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 2024呎 (4+房)
-$9,680万
-$47,826/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$8,300万
-$48,144/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,277万
-$31,537/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 2024呎 (4+房)
-$8,900万
-$43,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1724呎 (3房)
-$6,900万
-$40,023/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,254万
-$31,219/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 2141呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1725呎 (3房)
-$7,030万
-$40,754/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 2141呎 (4+房)
-$8,600万
-$40,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1725呎 (3房)
-$6,808万
-$39,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 722呎 (2房)
-$2,247万
-$31,122/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>St. George's Mansions - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>59 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>50 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3695呎 (4+房)
-$26,000万
-$70,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1871呎 (3房)
-$9,013万
-$48,172/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9,013万
-$51,444/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$17,765万
-$101,225/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$17,765万
-$101,398/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,690万
-$49,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,690万
-$49,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$9,328万
-$49,882/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9,388万
-$53,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,466万
-$34,112/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,450万
-$48,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,550万
-$48,801/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,417万
-$33,436/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,575万
-$48,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,675万
-$49,515/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8,960万
-$47,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$9,060万
-$48,501/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,345万
-$32,430/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,149万
-$46,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,250万
-$47,089/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-$2,381万
-$31,170/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,800万
-$50,142/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$9,500万
-$54,224/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,280万
-$31,535/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,635万
-$49,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,726万
-$49,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,258万
-$31,231/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8,060万
-$43,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,140万
-$46,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8,600万
-$45,989/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8,638万
-$46,242/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,266万
-$31,342/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,300万
-$47,293/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8,184万
-$43,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,352万
-$32,531/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8,000万
-$42,781/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1868呎 (3房)
-$8,200万
-$43,897/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,322万
-$32,116/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$8,808万
-$50,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$8,140万
-$46,461/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$8,100万
-$43,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$7,580万
-$43,265/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,185万
-$30,221/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1870呎 (3房)
-$6,800万
-$36,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6,800万
-$38,813/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$6,500万
-$37,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6,660万
-$38,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 764呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1755呎 (3房)
-$6,600万
-$37,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1752呎 (3房)
-$6,800万
-$38,813/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 723呎 (2房)
-$2,247万
-$31,079/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>St. George's Mansions - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>58 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>57 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3325呎 (4+房)
-$23,280万
-$70,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,702万
-$36,913/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 3325呎 (4+房)
-$21,800万
-$65,564/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,648万
-$36,174/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 2087呎 (4+房)
-$19,300万
-$92,477/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1840呎 (3房)
-$19,300万
-$104,891/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 772呎 (2房)
-$2,854万
-$36,969/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1973呎 (4+房)
-$11,300万
-$57,273/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1840呎 (3房)
-$8,339万
-$45,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,518万
-$34,399/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$9,868万
-$50,041/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$8,125万
-$47,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,475万
-$33,807/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$9,800万
-$49,696/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$8,000万
-$46,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,431万
-$33,210/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$9,569万
-$48,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,850万
-$45,587/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,395万
-$32,719/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$9,480万
-$48,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,690万
-$44,657/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,357万
-$32,199/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$9,100万
-$46,146/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,580万
-$44,019/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,350万
-$32,104/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 2088呎 (4+房)
-$8,900万
-$42,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,480万
-$43,438/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,315万
-$31,626/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,850万
-$44,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,400万
-$42,973/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,280万
-$31,148/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,800万
-$44,625/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,360万
-$42,741/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,425万
-$33,128/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,738万
-$44,310/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,288万
-$42,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 772呎 (2房)
-$2,738万
-$35,466/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,638万
-$43,803/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,200万
-$41,812/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,175万
-$29,713/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,548万
-$43,347/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,000万
-$40,650/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,140万
-$29,235/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,350万
-$42,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$7,245万
-$42,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 772呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$8,020万
-$40,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$6,750万
-$39,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,265万
-$30,943/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1972呎 (4+房)
-$7,780万
-$39,452/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1722呎 (3房)
-$6,520万
-$37,863/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,076万
-$28,361/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1973呎 (4+房)
-$7,628万
-$38,662/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1723呎 (3房)
-$6,380万
-$37,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 732呎 (2房)
-$2,055万
-$28,074/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1973呎 (4+房)
-$7,800万
-$39,534/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1723呎 (3房)
-$6,450万
-$37,435/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 772呎 (2房)
-$2,280万
-$29,534/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8659,4 +8840,2180 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3330呎 (4+房)
+$23800万
+$71,471/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2674万
+$37,036/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 3330呎 (4+房)
+$21380万
+$64,204/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2620万
+$36,288/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2141呎 (4+房)
+$12168万
+$56,833/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1842呎 (3房)
+$9512万
+$51,640/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+$2544万
+$33,300/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 2141呎 (4+房)
+$12018万
+$56,133/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1725呎 (3房)
+$9210万
+$53,391/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2705万
+$37,465/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11900万
+$55,607/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8800万
+$51,044/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2466万
+$34,157/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 2024呎 (4+房)
+$11800万
+$58,300/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8600万
+$49,884/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11700万
+$54,673/呎
+(21年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8500万
+$49,304/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2382万
+$32,992/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11500万
+$53,738/呎
+(20年-09月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1841呎 (3房)
+$9000万
+$48,886/呎
+(20年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2340万
+$32,410/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11500万
+$53,738/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8380万
+$48,608/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11300万
+$52,804/呎
+(22年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8280万
+$48,028/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2463万
+$34,111/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$11000万
+$51,402/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1841呎 (3房)
+$8900万
+$48,343/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2510万
+$34,765/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$10500万
+$49,065/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8274万
+$47,993/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2222万
+$30,776/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$10280万
+$48,037/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$7950万
+$46,114/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$10270万
+$47,991/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$7838万
+$45,464/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2178万
+$30,169/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$10450万
+$48,832/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1841呎 (3房)
+$8600万
+$46,714/呎
+(23年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2150万
+$29,778/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 2140呎 (4+房)
+$9780万
+$45,701/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1841呎 (3房)
+$8020万
+$43,563/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 2024呎 (4+房)
+$9680万
+$47,826/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$8300万
+$48,144/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2277万
+$31,537/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 2024呎 (4+房)
+$8900万
+$43,972/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1724呎 (3房)
+$6900万
+$40,023/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2254万
+$31,219/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 2141呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1725呎 (3房)
+$7030万
+$40,754/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 2141呎 (4+房)
+$8600万
+$40,168/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1725呎 (3房)
+$6808万
+$39,467/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 722呎 (2房)
+$2247万
+$31,122/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3695呎 (4+房)
+$26000万
+$70,365/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1871呎 (3房)
+$9013万
+$48,172/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9013万
+$51,444/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$17765万
+$101,225/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$17765万
+$101,398/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8690万
+$49,516/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8690万
+$49,600/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$9328万
+$49,882/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9388万
+$53,584/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2466万
+$34,112/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8450万
+$48,148/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8550万
+$48,801/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2417万
+$33,436/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8575万
+$48,860/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8675万
+$49,515/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8960万
+$47,914/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$9060万
+$48,501/呎
+(21年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2345万
+$32,430/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8149万
+$46,433/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8250万
+$47,089/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+$2381万
+$31,170/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8800万
+$50,142/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$9500万
+$54,224/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2280万
+$31,535/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8635万
+$49,202/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8726万
+$49,806/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2258万
+$31,231/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8060万
+$43,102/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8140万
+$46,461/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8600万
+$45,989/呎
+(20年-08月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8638万
+$46,242/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2266万
+$31,342/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8300万
+$47,293/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8184万
+$43,810/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2352万
+$32,531/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8000万
+$42,781/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1868呎 (3房)
+$8200万
+$43,897/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2322万
+$32,116/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$8808万
+$50,188/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$8140万
+$46,461/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$8100万
+$43,316/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$7580万
+$43,265/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2185万
+$30,221/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1870呎 (3房)
+$6800万
+$36,364/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6800万
+$38,813/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$6500万
+$37,037/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6660万
+$38,014/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 764呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1755呎 (3房)
+$6600万
+$37,607/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1752呎 (3房)
+$6800万
+$38,813/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 723呎 (2房)
+$2247万
+$31,079/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3325呎 (4+房)
+$23280万
+$70,015/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2702万
+$36,913/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 3325呎 (4+房)
+$21800万
+$65,564/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2648万
+$36,174/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 2087呎 (4+房)
+$19300万
+$92,477/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1840呎 (3房)
+$19300万
+$104,891/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 772呎 (2房)
+$2854万
+$36,969/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1973呎 (4+房)
+$11300万
+$57,273/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1840呎 (3房)
+$8339万
+$45,322/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2518万
+$34,399/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$9868万
+$50,041/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$8125万
+$47,185/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2475万
+$33,807/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$9800万
+$49,696/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$8000万
+$46,458/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2431万
+$33,210/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$9569万
+$48,523/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7850万
+$45,587/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2395万
+$32,719/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$9480万
+$48,073/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7690万
+$44,657/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2357万
+$32,199/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$9100万
+$46,146/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7580万
+$44,019/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2350万
+$32,104/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 2088呎 (4+房)
+$8900万
+$42,625/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7480万
+$43,438/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2315万
+$31,626/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8850万
+$44,878/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7400万
+$42,973/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2280万
+$31,148/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8800万
+$44,625/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7360万
+$42,741/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2425万
+$33,128/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8738万
+$44,310/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7288万
+$42,323/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 772呎 (2房)
+$2738万
+$35,466/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8638万
+$43,803/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7200万
+$41,812/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2175万
+$29,713/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8548万
+$43,347/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7000万
+$40,650/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2140万
+$29,235/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8350万
+$42,343/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$7245万
+$42,073/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 772呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$8020万
+$40,669/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$6750万
+$39,199/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2265万
+$30,943/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1972呎 (4+房)
+$7780万
+$39,452/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1722呎 (3房)
+$6520万
+$37,863/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2076万
+$28,361/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1973呎 (4+房)
+$7628万
+$38,662/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1723呎 (3房)
+$6380万
+$37,028/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 732呎 (2房)
+$2055万
+$28,074/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1973呎 (4+房)
+$7800万
+$39,534/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1723呎 (3房)
+$6450万
+$37,435/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 772呎 (2房)
+$2280万
+$29,534/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2140</v>
+        <v>2024</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>119000000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>55607</v>
+        <v>58794</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -9068,9 +9068,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 2140呎 (4+房)
+          <t>A | 2024呎 (4+房)
 $11900万
-$55,607/呎
+$58,794/呎
 (23年-03月)</t>
         </is>
       </c>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:N177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -715,6 +719,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -761,6 +785,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -807,6 +851,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -853,6 +917,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -899,6 +983,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -945,6 +1049,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -991,6 +1115,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1037,6 +1181,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1083,6 +1247,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1129,6 +1313,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1175,6 +1379,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1221,6 +1445,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1267,6 +1511,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1313,6 +1577,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1363,6 +1647,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1409,6 +1713,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1455,6 +1779,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1501,6 +1845,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1547,6 +1911,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1593,6 +1977,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1639,6 +2043,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1685,6 +2109,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1731,6 +2175,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1781,6 +2245,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1827,6 +2311,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1873,6 +2377,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1919,6 +2443,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1965,6 +2509,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2011,6 +2575,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2057,6 +2641,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2103,6 +2707,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2149,6 +2773,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2195,6 +2839,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2241,6 +2905,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2287,6 +2971,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2337,6 +3041,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2383,6 +3107,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2429,6 +3173,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2475,6 +3239,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2521,6 +3305,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2567,6 +3371,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2613,6 +3437,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2659,6 +3503,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2705,6 +3569,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2755,6 +3639,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2801,6 +3705,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2847,6 +3771,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2893,6 +3837,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2939,6 +3903,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2985,6 +3969,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3031,6 +4035,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3077,6 +4101,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3123,6 +4167,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3173,6 +4237,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3219,6 +4303,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3269,6 +4373,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3315,6 +4439,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3361,6 +4505,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3407,6 +4571,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3457,6 +4641,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3503,6 +4707,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3553,6 +4777,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3599,6 +4843,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3645,6 +4909,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3695,6 +4979,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3741,6 +5045,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3787,6 +5111,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3837,6 +5181,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3883,6 +5247,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3929,6 +5313,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3975,6 +5379,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4021,6 +5445,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4067,6 +5511,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4113,6 +5577,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4159,6 +5643,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4205,6 +5709,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4255,6 +5779,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4301,6 +5845,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4347,6 +5911,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4393,6 +5977,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4439,6 +6043,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4485,6 +6109,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4531,6 +6175,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4577,6 +6241,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4623,6 +6307,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4669,6 +6373,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4715,6 +6439,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4761,6 +6505,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4807,6 +6571,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4853,6 +6637,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4899,6 +6703,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4949,6 +6773,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4995,6 +6839,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5041,6 +6905,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5087,6 +6971,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5133,6 +7037,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5179,6 +7103,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5225,6 +7169,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5271,6 +7235,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5317,6 +7301,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5363,6 +7367,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5409,6 +7433,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5455,6 +7499,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5505,6 +7569,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5551,6 +7635,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5597,6 +7701,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5643,6 +7767,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5689,6 +7833,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5735,6 +7899,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5785,6 +7969,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5831,6 +8035,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5877,6 +8101,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5927,6 +8171,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -5973,6 +8237,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6019,6 +8303,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6065,6 +8369,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6111,6 +8435,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6157,6 +8501,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6203,6 +8567,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6249,6 +8633,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6295,6 +8699,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6341,6 +8765,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6367,7 +8811,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -6376,16 +8820,36 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
         <v>28540000</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>36969</v>
+        <v>38989</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -6433,6 +8897,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6479,6 +8963,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6525,6 +9029,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6571,6 +9095,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6617,6 +9161,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6663,6 +9227,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6709,6 +9293,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6755,6 +9359,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6801,6 +9425,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6847,6 +9491,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6893,6 +9557,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6939,6 +9623,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6985,6 +9689,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7031,6 +9755,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7077,6 +9821,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7123,6 +9887,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7169,6 +9953,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7215,6 +10019,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7261,6 +10085,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7307,6 +10151,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7353,6 +10217,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7399,6 +10283,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7445,6 +10349,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7491,6 +10415,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7537,6 +10481,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7583,6 +10547,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7629,6 +10613,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7675,6 +10679,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7721,6 +10745,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7747,7 +10791,7 @@
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>772</v>
+        <v>732</v>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
@@ -7756,16 +10800,36 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
         <v>27380000</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>35466</v>
+        <v>37404</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -7813,6 +10877,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7859,6 +10943,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7905,6 +11009,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7951,6 +11075,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7997,6 +11141,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8043,6 +11207,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8089,6 +11273,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8135,6 +11339,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8185,6 +11409,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -8231,6 +11475,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8277,6 +11541,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8323,6 +11607,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8369,6 +11673,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8415,6 +11739,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8461,6 +11805,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8507,6 +11871,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8553,6 +11937,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8599,6 +12003,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8645,6 +12069,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8691,6 +12135,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8737,6 +12201,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8783,6 +12267,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8829,13 +12333,33 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -8961,7 +12485,7 @@
           <t>A | 3330呎 (4+房)
 $23800万
 $71,471/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -8970,7 +12494,7 @@
           <t>C | 722呎 (2房)
 $2674万
 $37,036/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -8985,7 +12509,7 @@
           <t>A | 3330呎 (4+房)
 $21380万
 $64,204/呎
-(21年-04月)</t>
+(21年-04月-18日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -8994,7 +12518,7 @@
           <t>C | 722呎 (2房)
 $2620万
 $36,288/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -9009,7 +12533,7 @@
           <t>A | 2141呎 (4+房)
 $12168万
 $56,833/呎
-(23年-05月)</t>
+(23年-05月-14日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9017,7 +12541,7 @@
           <t>B | 1842呎 (3房)
 $9512万
 $51,640/呎
-(23年-05月)</t>
+(23年-05月-14日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -9025,7 +12549,7 @@
           <t>C | 764呎 (2房)
 $2544万
 $33,300/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -9040,7 +12564,7 @@
           <t>A | 2141呎 (4+房)
 $12018万
 $56,133/呎
-(23年-04月)</t>
+(23年-04月-16日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9048,7 +12572,7 @@
           <t>B | 1725呎 (3房)
 $9210万
 $53,391/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -9056,7 +12580,7 @@
           <t>C | 722呎 (2房)
 $2705万
 $37,465/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -9071,7 +12595,7 @@
           <t>A | 2024呎 (4+房)
 $11900万
 $58,794/呎
-(23年-03月)</t>
+(23年-03月-29日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9079,7 +12603,7 @@
           <t>B | 1724呎 (3房)
 $8800万
 $51,044/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -9087,7 +12611,7 @@
           <t>C | 722呎 (2房)
 $2466万
 $34,157/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -9102,7 +12626,7 @@
           <t>A | 2024呎 (4+房)
 $11800万
 $58,300/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9110,7 +12634,7 @@
           <t>B | 1724呎 (3房)
 $8600万
 $49,884/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -9133,7 +12657,7 @@
           <t>A | 2140呎 (4+房)
 $11700万
 $54,673/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9141,7 +12665,7 @@
           <t>B | 1724呎 (3房)
 $8500万
 $49,304/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9149,7 +12673,7 @@
           <t>C | 722呎 (2房)
 $2382万
 $32,992/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -9164,7 +12688,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(20年-09月)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9172,7 +12696,7 @@
           <t>B | 1841呎 (3房)
 $9000万
 $48,886/呎
-(20年-12月)</t>
+(20年-12月-17日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9180,7 +12704,7 @@
           <t>C | 722呎 (2房)
 $2340万
 $32,410/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -9195,7 +12719,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9203,7 +12727,7 @@
           <t>B | 1724呎 (3房)
 $8380万
 $48,608/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9226,7 +12750,7 @@
           <t>A | 2140呎 (4+房)
 $11300万
 $52,804/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9234,7 +12758,7 @@
           <t>B | 1724呎 (3房)
 $8280万
 $48,028/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9242,7 +12766,7 @@
           <t>C | 722呎 (2房)
 $2463万
 $34,111/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -9257,7 +12781,7 @@
           <t>A | 2140呎 (4+房)
 $11000万
 $51,402/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9265,7 +12789,7 @@
           <t>B | 1841呎 (3房)
 $8900万
 $48,343/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -9273,7 +12797,7 @@
           <t>C | 722呎 (2房)
 $2510万
 $34,765/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -9288,7 +12812,7 @@
           <t>A | 2140呎 (4+房)
 $10500万
 $49,065/呎
-(22年-05月)</t>
+(22年-05月-30日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9296,7 +12820,7 @@
           <t>B | 1724呎 (3房)
 $8274万
 $47,993/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9304,7 +12828,7 @@
           <t>C | 722呎 (2房)
 $2222万
 $30,776/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -9319,7 +12843,7 @@
           <t>A | 2140呎 (4+房)
 $10280万
 $48,037/呎
-(22年-05月)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -9327,7 +12851,7 @@
           <t>B | 1724呎 (3房)
 $7950万
 $46,114/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -9350,7 +12874,7 @@
           <t>A | 2140呎 (4+房)
 $10270万
 $47,991/呎
-(23年-01月)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9358,7 +12882,7 @@
           <t>B | 1724呎 (3房)
 $7838万
 $45,464/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9366,7 +12890,7 @@
           <t>C | 722呎 (2房)
 $2178万
 $30,169/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -9381,7 +12905,7 @@
           <t>A | 2140呎 (4+房)
 $10450万
 $48,832/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9389,7 +12913,7 @@
           <t>B | 1841呎 (3房)
 $8600万
 $46,714/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -9397,7 +12921,7 @@
           <t>C | 722呎 (2房)
 $2150万
 $29,778/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -9412,7 +12936,7 @@
           <t>A | 2140呎 (4+房)
 $9780万
 $45,701/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9420,7 +12944,7 @@
           <t>B | 1841呎 (3房)
 $8020万
 $43,563/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -9443,7 +12967,7 @@
           <t>A | 2024呎 (4+房)
 $9680万
 $47,826/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -9451,7 +12975,7 @@
           <t>B | 1724呎 (3房)
 $8300万
 $48,144/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -9459,7 +12983,7 @@
           <t>C | 722呎 (2房)
 $2277万
 $31,537/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -9474,7 +12998,7 @@
           <t>A | 2024呎 (4+房)
 $8900万
 $43,972/呎
-(23年-12月)</t>
+(23年-12月-05日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -9482,7 +13006,7 @@
           <t>B | 1724呎 (3房)
 $6900万
 $40,023/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9490,7 +13014,7 @@
           <t>C | 722呎 (2房)
 $2254万
 $31,219/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -9513,7 +13037,7 @@
           <t>B | 1725呎 (3房)
 $7030万
 $40,754/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -9536,7 +13060,7 @@
           <t>A | 2141呎 (4+房)
 $8600万
 $40,168/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9544,7 +13068,7 @@
           <t>B | 1725呎 (3房)
 $6808万
 $39,467/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9552,7 +13076,7 @@
           <t>C | 722呎 (2房)
 $2247万
 $31,122/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -9684,7 +13208,7 @@
           <t>A | 3695呎 (4+房)
 $26000万
 $70,365/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -9708,7 +13232,7 @@
           <t>A | 1871呎 (3房)
 $9013万
 $48,172/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -9716,7 +13240,7 @@
           <t>B | 1752呎 (3房)
 $9013万
 $51,444/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -9739,7 +13263,7 @@
           <t>A | 1755呎 (3房)
 $17765万
 $101,225/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -9747,7 +13271,7 @@
           <t>B | 1752呎 (3房)
 $17765万
 $101,398/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -9770,7 +13294,7 @@
           <t>A | 1755呎 (3房)
 $8690万
 $49,516/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -9778,7 +13302,7 @@
           <t>B | 1752呎 (3房)
 $8690万
 $49,600/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9801,7 +13325,7 @@
           <t>A | 1870呎 (3房)
 $9328万
 $49,882/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9809,7 +13333,7 @@
           <t>B | 1752呎 (3房)
 $9388万
 $53,584/呎
-(23年-02月)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -9817,7 +13341,7 @@
           <t>C | 723呎 (2房)
 $2466万
 $34,112/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -9832,7 +13356,7 @@
           <t>A | 1755呎 (3房)
 $8450万
 $48,148/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9840,7 +13364,7 @@
           <t>B | 1752呎 (3房)
 $8550万
 $48,801/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -9848,7 +13372,7 @@
           <t>C | 723呎 (2房)
 $2417万
 $33,436/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -9863,7 +13387,7 @@
           <t>A | 1755呎 (3房)
 $8575万
 $48,860/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9871,7 +13395,7 @@
           <t>B | 1752呎 (3房)
 $8675万
 $49,515/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9894,7 +13418,7 @@
           <t>A | 1870呎 (3房)
 $8960万
 $47,914/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9902,7 +13426,7 @@
           <t>B | 1868呎 (3房)
 $9060万
 $48,501/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9910,7 +13434,7 @@
           <t>C | 723呎 (2房)
 $2345万
 $32,430/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -9925,7 +13449,7 @@
           <t>A | 1755呎 (3房)
 $8149万
 $46,433/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9933,7 +13457,7 @@
           <t>B | 1752呎 (3房)
 $8250万
 $47,089/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -9941,7 +13465,7 @@
           <t>C | 764呎 (2房)
 $2381万
 $31,170/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -9956,7 +13480,7 @@
           <t>A | 1755呎 (3房)
 $8800万
 $50,142/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9964,7 +13488,7 @@
           <t>B | 1752呎 (3房)
 $9500万
 $54,224/呎
-(24年-07月)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9972,7 +13496,7 @@
           <t>C | 723呎 (2房)
 $2280万
 $31,535/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -9987,7 +13511,7 @@
           <t>A | 1755呎 (3房)
 $8635万
 $49,202/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9995,7 +13519,7 @@
           <t>B | 1752呎 (3房)
 $8726万
 $49,806/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -10003,7 +13527,7 @@
           <t>C | 723呎 (2房)
 $2258万
 $31,231/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -10018,7 +13542,7 @@
           <t>A | 1870呎 (3房)
 $8060万
 $43,102/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -10026,7 +13550,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -10049,7 +13573,7 @@
           <t>A | 1870呎 (3房)
 $8600万
 $45,989/呎
-(20年-08月)</t>
+(20年-08月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -10057,7 +13581,7 @@
           <t>B | 1868呎 (3房)
 $8638万
 $46,242/呎
-(23年-03月)</t>
+(23年-03月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -10065,7 +13589,7 @@
           <t>C | 723呎 (2房)
 $2266万
 $31,342/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -10080,7 +13604,7 @@
           <t>A | 1755呎 (3房)
 $8300万
 $47,293/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -10088,7 +13612,7 @@
           <t>B | 1868呎 (3房)
 $8184万
 $43,810/呎
-(23年-07月)</t>
+(23年-07月-02日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -10096,7 +13620,7 @@
           <t>C | 723呎 (2房)
 $2352万
 $32,531/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -10111,7 +13635,7 @@
           <t>A | 1870呎 (3房)
 $8000万
 $42,781/呎
-(22年-05月)</t>
+(22年-05月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -10119,7 +13643,7 @@
           <t>B | 1868呎 (3房)
 $8200万
 $43,897/呎
-(23年-03月)</t>
+(23年-03月-27日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -10127,7 +13651,7 @@
           <t>C | 723呎 (2房)
 $2322万
 $32,116/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -10142,7 +13666,7 @@
           <t>A | 1755呎 (3房)
 $8808万
 $50,188/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -10150,7 +13674,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10173,7 +13697,7 @@
           <t>A | 1870呎 (3房)
 $8100万
 $43,316/呎
-(23年-03月)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10181,7 +13705,7 @@
           <t>B | 1752呎 (3房)
 $7580万
 $43,265/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -10189,7 +13713,7 @@
           <t>C | 723呎 (2房)
 $2185万
 $30,221/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -10204,7 +13728,7 @@
           <t>A | 1870呎 (3房)
 $6800万
 $36,364/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10212,7 +13736,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10235,7 +13759,7 @@
           <t>A | 1755呎 (3房)
 $6500万
 $37,037/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -10243,7 +13767,7 @@
           <t>B | 1752呎 (3房)
 $6660万
 $38,014/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10266,7 +13790,7 @@
           <t>A | 1755呎 (3房)
 $6600万
 $37,607/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10274,7 +13798,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10282,7 +13806,7 @@
           <t>C | 723呎 (2房)
 $2247万
 $31,079/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -10414,7 +13938,7 @@
           <t>A | 3325呎 (4+房)
 $23280万
 $70,015/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -10423,7 +13947,7 @@
           <t>C | 732呎 (2房)
 $2702万
 $36,913/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -10438,7 +13962,7 @@
           <t>A | 3325呎 (4+房)
 $21800万
 $65,564/呎
-(22年-02月)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -10447,7 +13971,7 @@
           <t>C | 732呎 (2房)
 $2648万
 $36,174/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -10462,7 +13986,7 @@
           <t>A | 2087呎 (4+房)
 $19300万
 $92,477/呎
-(24年-09月)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -10470,15 +13994,15 @@
           <t>B | 1840呎 (3房)
 $19300万
 $104,891/呎
-(24年-09月)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 772呎 (2房)
+          <t>C | 732呎 (2房)
 $2854万
-$36,969/呎
-(26年-06月)</t>
+$38,989/呎
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -10493,7 +14017,7 @@
           <t>A | 1973呎 (4+房)
 $11300万
 $57,273/呎
-(23年-05月)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -10501,7 +14025,7 @@
           <t>B | 1840呎 (3房)
 $8339万
 $45,322/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -10509,7 +14033,7 @@
           <t>C | 732呎 (2房)
 $2518万
 $34,399/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -10524,7 +14048,7 @@
           <t>A | 1972呎 (4+房)
 $9868万
 $50,041/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -10532,7 +14056,7 @@
           <t>B | 1722呎 (3房)
 $8125万
 $47,185/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -10540,7 +14064,7 @@
           <t>C | 732呎 (2房)
 $2475万
 $33,807/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -10555,7 +14079,7 @@
           <t>A | 1972呎 (4+房)
 $9800万
 $49,696/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -10563,7 +14087,7 @@
           <t>B | 1722呎 (3房)
 $8000万
 $46,458/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -10571,7 +14095,7 @@
           <t>C | 732呎 (2房)
 $2431万
 $33,210/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -10586,7 +14110,7 @@
           <t>A | 1972呎 (4+房)
 $9569万
 $48,523/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -10594,7 +14118,7 @@
           <t>B | 1722呎 (3房)
 $7850万
 $45,587/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -10602,7 +14126,7 @@
           <t>C | 732呎 (2房)
 $2395万
 $32,719/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -10617,7 +14141,7 @@
           <t>A | 1972呎 (4+房)
 $9480万
 $48,073/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -10625,7 +14149,7 @@
           <t>B | 1722呎 (3房)
 $7690万
 $44,657/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -10633,7 +14157,7 @@
           <t>C | 732呎 (2房)
 $2357万
 $32,199/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -10648,7 +14172,7 @@
           <t>A | 1972呎 (4+房)
 $9100万
 $46,146/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -10656,7 +14180,7 @@
           <t>B | 1722呎 (3房)
 $7580万
 $44,019/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -10664,7 +14188,7 @@
           <t>C | 732呎 (2房)
 $2350万
 $32,104/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -10679,7 +14203,7 @@
           <t>A | 2088呎 (4+房)
 $8900万
 $42,625/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -10687,7 +14211,7 @@
           <t>B | 1722呎 (3房)
 $7480万
 $43,438/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -10695,7 +14219,7 @@
           <t>C | 732呎 (2房)
 $2315万
 $31,626/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -10710,7 +14234,7 @@
           <t>A | 1972呎 (4+房)
 $8850万
 $44,878/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -10718,7 +14242,7 @@
           <t>B | 1722呎 (3房)
 $7400万
 $42,973/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -10726,7 +14250,7 @@
           <t>C | 732呎 (2房)
 $2280万
 $31,148/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -10741,7 +14265,7 @@
           <t>A | 1972呎 (4+房)
 $8800万
 $44,625/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -10749,7 +14273,7 @@
           <t>B | 1722呎 (3房)
 $7360万
 $42,741/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -10757,7 +14281,7 @@
           <t>C | 732呎 (2房)
 $2425万
 $33,128/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -10772,7 +14296,7 @@
           <t>A | 1972呎 (4+房)
 $8738万
 $44,310/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -10780,15 +14304,15 @@
           <t>B | 1722呎 (3房)
 $7288万
 $42,323/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 772呎 (2房)
+          <t>C | 732呎 (2房)
 $2738万
-$35,466/呎
-(26年-06月)</t>
+$37,404/呎
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -10803,7 +14327,7 @@
           <t>A | 1972呎 (4+房)
 $8638万
 $43,803/呎
-(24年-08月)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -10811,7 +14335,7 @@
           <t>B | 1722呎 (3房)
 $7200万
 $41,812/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -10819,7 +14343,7 @@
           <t>C | 732呎 (2房)
 $2175万
 $29,713/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -10834,7 +14358,7 @@
           <t>A | 1972呎 (4+房)
 $8548万
 $43,347/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -10842,7 +14366,7 @@
           <t>B | 1722呎 (3房)
 $7000万
 $40,650/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -10850,7 +14374,7 @@
           <t>C | 732呎 (2房)
 $2140万
 $29,235/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -10865,7 +14389,7 @@
           <t>A | 1972呎 (4+房)
 $8350万
 $42,343/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -10873,7 +14397,7 @@
           <t>B | 1722呎 (3房)
 $7245万
 $42,073/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10896,7 +14420,7 @@
           <t>A | 1972呎 (4+房)
 $8020万
 $40,669/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10904,7 +14428,7 @@
           <t>B | 1722呎 (3房)
 $6750万
 $39,199/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -10912,7 +14436,7 @@
           <t>C | 732呎 (2房)
 $2265万
 $30,943/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -10927,7 +14451,7 @@
           <t>A | 1972呎 (4+房)
 $7780万
 $39,452/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10935,7 +14459,7 @@
           <t>B | 1722呎 (3房)
 $6520万
 $37,863/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10943,7 +14467,7 @@
           <t>C | 732呎 (2房)
 $2076万
 $28,361/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -10958,7 +14482,7 @@
           <t>A | 1973呎 (4+房)
 $7628万
 $38,662/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -10966,7 +14490,7 @@
           <t>B | 1723呎 (3房)
 $6380万
 $37,028/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -10974,7 +14498,7 @@
           <t>C | 732呎 (2房)
 $2055万
 $28,074/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -10989,7 +14513,7 @@
           <t>A | 1973呎 (4+房)
 $7800万
 $39,534/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10997,7 +14521,7 @@
           <t>B | 1723呎 (3房)
 $6450万
 $37,435/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -11005,7 +14529,7 @@
           <t>C | 772呎 (2房)
 $2280万
 $29,534/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -4353,23 +4353,19 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>93000000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>43438</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4378,12 +4374,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4393,7 +4389,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12424,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -12438,7 +12434,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -13024,12 +13020,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 2141呎 (4+房)
-招标单位
--
-(在售)</t>
+$9300万
+$43,438/呎
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -12481,7 +12481,7 @@
           <t>A | 3330呎 (4+房)
 $23800万
 $71,471/呎
-(20年-11月-11日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -12490,7 +12490,7 @@
           <t>C | 722呎 (2房)
 $2674万
 $37,036/呎
-(24年-09月-10日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
           <t>A | 3330呎 (4+房)
 $21380万
 $64,204/呎
-(21年-04月-18日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -12514,7 +12514,7 @@
           <t>C | 722呎 (2房)
 $2620万
 $36,288/呎
-(25年-10月-30日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
           <t>A | 2141呎 (4+房)
 $12168万
 $56,833/呎
-(23年-05月-14日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12537,7 +12537,7 @@
           <t>B | 1842呎 (3房)
 $9512万
 $51,640/呎
-(23年-05月-14日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>C | 764呎 (2房)
 $2544万
 $33,300/呎
-(24年-09月-02日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
           <t>A | 2141呎 (4+房)
 $12018万
 $56,133/呎
-(23年-04月-16日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>B | 1725呎 (3房)
 $9210万
 $53,391/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>C | 722呎 (2房)
 $2705万
 $37,465/呎
-(26年-06月-09日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
           <t>A | 2024呎 (4+房)
 $11900万
 $58,794/呎
-(23年-03月-29日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -12599,7 +12599,7 @@
           <t>B | 1724呎 (3房)
 $8800万
 $51,044/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -12607,7 +12607,7 @@
           <t>C | 722呎 (2房)
 $2466万
 $34,157/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
           <t>A | 2024呎 (4+房)
 $11800万
 $58,300/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -12630,7 +12630,7 @@
           <t>B | 1724呎 (3房)
 $8600万
 $49,884/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -12653,7 +12653,7 @@
           <t>A | 2140呎 (4+房)
 $11700万
 $54,673/呎
-(21年-10月-06日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12661,7 +12661,7 @@
           <t>B | 1724呎 (3房)
 $8500万
 $49,304/呎
-(25年-02月-12日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -12669,7 +12669,7 @@
           <t>C | 722呎 (2房)
 $2382万
 $32,992/呎
-(25年-06月-01日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(20年-09月-09日)</t>
+(20年-09月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12692,7 +12692,7 @@
           <t>B | 1841呎 (3房)
 $9000万
 $48,886/呎
-(20年-12月-17日)</t>
+(20年-12月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -12700,7 +12700,7 @@
           <t>C | 722呎 (2房)
 $2340万
 $32,410/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12715,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(23年-01月-31日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -12723,7 +12723,7 @@
           <t>B | 1724呎 (3房)
 $8380万
 $48,608/呎
-(25年-01月-09日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12746,7 +12746,7 @@
           <t>A | 2140呎 (4+房)
 $11300万
 $52,804/呎
-(22年-09月-25日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12754,7 +12754,7 @@
           <t>B | 1724呎 (3房)
 $8280万
 $48,028/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12762,7 +12762,7 @@
           <t>C | 722呎 (2房)
 $2463万
 $34,111/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
           <t>A | 2140呎 (4+房)
 $11000万
 $51,402/呎
-(23年-01月-19日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12785,7 +12785,7 @@
           <t>B | 1841呎 (3房)
 $8900万
 $48,343/呎
-(23年-01月-19日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -12793,7 +12793,7 @@
           <t>C | 722呎 (2房)
 $2510万
 $34,765/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
           <t>A | 2140呎 (4+房)
 $10500万
 $49,065/呎
-(22年-05月-30日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12816,7 +12816,7 @@
           <t>B | 1724呎 (3房)
 $8274万
 $47,993/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -12824,7 +12824,7 @@
           <t>C | 722呎 (2房)
 $2222万
 $30,776/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12839,7 @@
           <t>A | 2140呎 (4+房)
 $10280万
 $48,037/呎
-(22年-05月-18日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12847,7 +12847,7 @@
           <t>B | 1724呎 (3房)
 $7950万
 $46,114/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -12870,7 +12870,7 @@
           <t>A | 2140呎 (4+房)
 $10270万
 $47,991/呎
-(23年-01月-26日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12878,7 +12878,7 @@
           <t>B | 1724呎 (3房)
 $7838万
 $45,464/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12886,7 +12886,7 @@
           <t>C | 722呎 (2房)
 $2178万
 $30,169/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -12901,7 +12901,7 @@
           <t>A | 2140呎 (4+房)
 $10450万
 $48,832/呎
-(23年-01月-30日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12909,7 +12909,7 @@
           <t>B | 1841呎 (3房)
 $8600万
 $46,714/呎
-(23年-01月-30日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -12917,7 +12917,7 @@
           <t>C | 722呎 (2房)
 $2150万
 $29,778/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
           <t>A | 2140呎 (4+房)
 $9780万
 $45,701/呎
-(23年-02月-07日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12940,7 +12940,7 @@
           <t>B | 1841呎 (3房)
 $8020万
 $43,563/呎
-(23年-02月-07日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12963,7 +12963,7 @@
           <t>A | 2024呎 (4+房)
 $9680万
 $47,826/呎
-(23年-08月-28日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -12971,7 +12971,7 @@
           <t>B | 1724呎 (3房)
 $8300万
 $48,144/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -12979,7 +12979,7 @@
           <t>C | 722呎 (2房)
 $2277万
 $31,537/呎
-(26年-07月-01日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
           <t>A | 2024呎 (4+房)
 $8900万
 $43,972/呎
-(23年-12月-05日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13002,7 +13002,7 @@
           <t>B | 1724呎 (3房)
 $6900万
 $40,023/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -13010,7 +13010,7 @@
           <t>C | 722呎 (2房)
 $2254万
 $31,219/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
           <t>A | 2141呎 (4+房)
 $9300万
 $43,438/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13033,7 +13033,7 @@
           <t>B | 1725呎 (3房)
 $7030万
 $40,754/呎
-(25年-10月-26日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -13056,7 +13056,7 @@
           <t>A | 2141呎 (4+房)
 $8600万
 $40,168/呎
-(25年-01月-13日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13064,7 +13064,7 @@
           <t>B | 1725呎 (3房)
 $6808万
 $39,467/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13072,7 +13072,7 @@
           <t>C | 722呎 (2房)
 $2247万
 $31,122/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
           <t>A | 3695呎 (4+房)
 $26000万
 $70,365/呎
-(21年-06月-29日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -13228,7 +13228,7 @@
           <t>A | 1871呎 (3房)
 $9013万
 $48,172/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -13236,7 +13236,7 @@
           <t>B | 1752呎 (3房)
 $9013万
 $51,444/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -13259,7 +13259,7 @@
           <t>A | 1755呎 (3房)
 $17765万
 $101,225/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13267,7 +13267,7 @@
           <t>B | 1752呎 (3房)
 $17765万
 $101,398/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -13290,7 +13290,7 @@
           <t>A | 1755呎 (3房)
 $8690万
 $49,516/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -13298,7 +13298,7 @@
           <t>B | 1752呎 (3房)
 $8690万
 $49,600/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -13321,7 +13321,7 @@
           <t>A | 1870呎 (3房)
 $9328万
 $49,882/呎
-(21年-07月-06日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -13329,7 +13329,7 @@
           <t>B | 1752呎 (3房)
 $9388万
 $53,584/呎
-(23年-02月-15日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -13337,7 +13337,7 @@
           <t>C | 723呎 (2房)
 $2466万
 $34,112/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
           <t>A | 1755呎 (3房)
 $8450万
 $48,148/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -13360,7 +13360,7 @@
           <t>B | 1752呎 (3房)
 $8550万
 $48,801/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -13368,7 +13368,7 @@
           <t>C | 723呎 (2房)
 $2417万
 $33,436/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
           <t>A | 1755呎 (3房)
 $8575万
 $48,860/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -13391,7 +13391,7 @@
           <t>B | 1752呎 (3房)
 $8675万
 $49,515/呎
-(25年-07月-09日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -13414,7 +13414,7 @@
           <t>A | 1870呎 (3房)
 $8960万
 $47,914/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -13422,7 +13422,7 @@
           <t>B | 1868呎 (3房)
 $9060万
 $48,501/呎
-(21年-06月-01日)</t>
+(21年-06月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -13430,7 +13430,7 @@
           <t>C | 723呎 (2房)
 $2345万
 $32,430/呎
-(24年-10月-09日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
           <t>A | 1755呎 (3房)
 $8149万
 $46,433/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -13453,7 +13453,7 @@
           <t>B | 1752呎 (3房)
 $8250万
 $47,089/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -13461,7 +13461,7 @@
           <t>C | 764呎 (2房)
 $2381万
 $31,170/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
           <t>A | 1755呎 (3房)
 $8800万
 $50,142/呎
-(25年-09月-22日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -13484,7 +13484,7 @@
           <t>B | 1752呎 (3房)
 $9500万
 $54,224/呎
-(24年-07月-22日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -13492,7 +13492,7 @@
           <t>C | 723呎 (2房)
 $2280万
 $31,535/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
           <t>A | 1755呎 (3房)
 $8635万
 $49,202/呎
-(23年-02月-02日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -13515,7 +13515,7 @@
           <t>B | 1752呎 (3房)
 $8726万
 $49,806/呎
-(23年-02月-02日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -13523,7 +13523,7 @@
           <t>C | 723呎 (2房)
 $2258万
 $31,231/呎
-(25年-02月-06日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
           <t>A | 1870呎 (3房)
 $8060万
 $43,102/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -13546,7 +13546,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -13569,7 +13569,7 @@
           <t>A | 1870呎 (3房)
 $8600万
 $45,989/呎
-(20年-08月-27日)</t>
+(20年-08月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -13577,7 +13577,7 @@
           <t>B | 1868呎 (3房)
 $8638万
 $46,242/呎
-(23年-03月-26日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -13585,7 +13585,7 @@
           <t>C | 723呎 (2房)
 $2266万
 $31,342/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
           <t>A | 1755呎 (3房)
 $8300万
 $47,293/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -13608,7 +13608,7 @@
           <t>B | 1868呎 (3房)
 $8184万
 $43,810/呎
-(23年-07月-02日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -13616,7 +13616,7 @@
           <t>C | 723呎 (2房)
 $2352万
 $32,531/呎
-(26年-06月-14日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -13631,7 +13631,7 @@
           <t>A | 1870呎 (3房)
 $8000万
 $42,781/呎
-(22年-05月-10日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -13639,7 +13639,7 @@
           <t>B | 1868呎 (3房)
 $8200万
 $43,897/呎
-(23年-03月-27日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -13647,7 +13647,7 @@
           <t>C | 723呎 (2房)
 $2322万
 $32,116/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
           <t>A | 1755呎 (3房)
 $8808万
 $50,188/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -13670,7 +13670,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -13693,7 +13693,7 @@
           <t>A | 1870呎 (3房)
 $8100万
 $43,316/呎
-(23年-03月-07日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -13701,7 +13701,7 @@
           <t>B | 1752呎 (3房)
 $7580万
 $43,265/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -13709,7 +13709,7 @@
           <t>C | 723呎 (2房)
 $2185万
 $30,221/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
           <t>A | 1870呎 (3房)
 $6800万
 $36,364/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13732,7 +13732,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -13755,7 +13755,7 @@
           <t>A | 1755呎 (3房)
 $6500万
 $37,037/呎
-(25年-05月-29日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13763,7 +13763,7 @@
           <t>B | 1752呎 (3房)
 $6660万
 $38,014/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -13786,7 +13786,7 @@
           <t>A | 1755呎 (3房)
 $6600万
 $37,607/呎
-(25年-05月-18日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13794,7 +13794,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13802,7 +13802,7 @@
           <t>C | 723呎 (2房)
 $2247万
 $31,079/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
           <t>A | 3325呎 (4+房)
 $23280万
 $70,015/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -13943,7 +13943,7 @@
           <t>C | 732呎 (2房)
 $2702万
 $36,913/呎
-(24年-09月-11日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
           <t>A | 3325呎 (4+房)
 $21800万
 $65,564/呎
-(22年-02月-09日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -13967,7 +13967,7 @@
           <t>C | 732呎 (2房)
 $2648万
 $36,174/呎
-(24年-09月-11日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
           <t>A | 2087呎 (4+房)
 $19300万
 $92,477/呎
-(24年-09月-19日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13990,7 +13990,7 @@
           <t>B | 1840呎 (3房)
 $19300万
 $104,891/呎
-(24年-09月-19日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -13998,7 +13998,7 @@
           <t>C | 732呎 (2房)
 $2854万
 $38,989/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
           <t>A | 1973呎 (4+房)
 $11300万
 $57,273/呎
-(23年-05月-09日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -14021,7 +14021,7 @@
           <t>B | 1840呎 (3房)
 $8339万
 $45,322/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -14029,7 +14029,7 @@
           <t>C | 732呎 (2房)
 $2518万
 $34,399/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
           <t>A | 1972呎 (4+房)
 $9868万
 $50,041/呎
-(24年-10月-07日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -14052,7 +14052,7 @@
           <t>B | 1722呎 (3房)
 $8125万
 $47,185/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14060,7 +14060,7 @@
           <t>C | 732呎 (2房)
 $2475万
 $33,807/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
           <t>A | 1972呎 (4+房)
 $9800万
 $49,696/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14083,7 +14083,7 @@
           <t>B | 1722呎 (3房)
 $8000万
 $46,458/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14091,7 +14091,7 @@
           <t>C | 732呎 (2房)
 $2431万
 $33,210/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
           <t>A | 1972呎 (4+房)
 $9569万
 $48,523/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14114,7 +14114,7 @@
           <t>B | 1722呎 (3房)
 $7850万
 $45,587/呎
-(25年-01月-13日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14122,7 +14122,7 @@
           <t>C | 732呎 (2房)
 $2395万
 $32,719/呎
-(25年-11月-20日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14137,7 @@
           <t>A | 1972呎 (4+房)
 $9480万
 $48,073/呎
-(24年-07月-25日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14145,7 +14145,7 @@
           <t>B | 1722呎 (3房)
 $7690万
 $44,657/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14153,7 +14153,7 @@
           <t>C | 732呎 (2房)
 $2357万
 $32,199/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
           <t>A | 1972呎 (4+房)
 $9100万
 $46,146/呎
-(24年-08月-26日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14176,7 +14176,7 @@
           <t>B | 1722呎 (3房)
 $7580万
 $44,019/呎
-(24年-08月-26日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14184,7 +14184,7 @@
           <t>C | 732呎 (2房)
 $2350万
 $32,104/呎
-(25年-01月-09日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
           <t>A | 2088呎 (4+房)
 $8900万
 $42,625/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -14207,7 +14207,7 @@
           <t>B | 1722呎 (3房)
 $7480万
 $43,438/呎
-(24年-07月-30日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -14215,7 +14215,7 @@
           <t>C | 732呎 (2房)
 $2315万
 $31,626/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
           <t>A | 1972呎 (4+房)
 $8850万
 $44,878/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -14238,7 +14238,7 @@
           <t>B | 1722呎 (3房)
 $7400万
 $42,973/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -14246,7 +14246,7 @@
           <t>C | 732呎 (2房)
 $2280万
 $31,148/呎
-(25年-11月-23日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
           <t>A | 1972呎 (4+房)
 $8800万
 $44,625/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -14269,7 +14269,7 @@
           <t>B | 1722呎 (3房)
 $7360万
 $42,741/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -14277,7 +14277,7 @@
           <t>C | 732呎 (2房)
 $2425万
 $33,128/呎
-(26年-06月-22日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
           <t>A | 1972呎 (4+房)
 $8738万
 $44,310/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -14300,7 +14300,7 @@
           <t>B | 1722呎 (3房)
 $7288万
 $42,323/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -14308,7 +14308,7 @@
           <t>C | 732呎 (2房)
 $2738万
 $37,404/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
           <t>A | 1972呎 (4+房)
 $8638万
 $43,803/呎
-(24年-08月-27日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -14331,7 +14331,7 @@
           <t>B | 1722呎 (3房)
 $7200万
 $41,812/呎
-(24年-03月-11日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -14339,7 +14339,7 @@
           <t>C | 732呎 (2房)
 $2175万
 $29,713/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
           <t>A | 1972呎 (4+房)
 $8548万
 $43,347/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -14362,7 +14362,7 @@
           <t>B | 1722呎 (3房)
 $7000万
 $40,650/呎
-(24年-07月-16日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -14370,7 +14370,7 @@
           <t>C | 732呎 (2房)
 $2140万
 $29,235/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
           <t>A | 1972呎 (4+房)
 $8350万
 $42,343/呎
-(24年-08月-26日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -14393,7 +14393,7 @@
           <t>B | 1722呎 (3房)
 $7245万
 $42,073/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -14416,7 +14416,7 @@
           <t>A | 1972呎 (4+房)
 $8020万
 $40,669/呎
-(25年-06月-18日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -14424,7 +14424,7 @@
           <t>B | 1722呎 (3房)
 $6750万
 $39,199/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -14432,7 +14432,7 @@
           <t>C | 732呎 (2房)
 $2265万
 $30,943/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
           <t>A | 1972呎 (4+房)
 $7780万
 $39,452/呎
-(24年-07月-07日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -14455,7 +14455,7 @@
           <t>B | 1722呎 (3房)
 $6520万
 $37,863/呎
-(24年-07月-17日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -14463,7 +14463,7 @@
           <t>C | 732呎 (2房)
 $2076万
 $28,361/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
           <t>A | 1973呎 (4+房)
 $7628万
 $38,662/呎
-(24年-09月-04日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -14486,7 +14486,7 @@
           <t>B | 1723呎 (3房)
 $6380万
 $37,028/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -14494,7 +14494,7 @@
           <t>C | 732呎 (2房)
 $2055万
 $28,074/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
           <t>A | 1973呎 (4+房)
 $7800万
 $39,534/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -14517,7 +14517,7 @@
           <t>B | 1723呎 (3房)
 $6450万
 $37,435/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -14525,7 +14525,7 @@
           <t>C | 772呎 (2房)
 $2280万
 $29,534/呎
-(25年-08月-18日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-st. george's mansions.xlsx
+++ b/files/九龙-何文田-st. george's mansions.xlsx
@@ -12481,7 +12481,7 @@
           <t>A | 3330呎 (4+房)
 $23800万
 $71,471/呎
-(20年-11月)</t>
+(20年-11月-11日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -12490,7 +12490,7 @@
           <t>C | 722呎 (2房)
 $2674万
 $37,036/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12505,7 @@
           <t>A | 3330呎 (4+房)
 $21380万
 $64,204/呎
-(21年-04月)</t>
+(21年-04月-18日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -12514,7 +12514,7 @@
           <t>C | 722呎 (2房)
 $2620万
 $36,288/呎
-(25年-10月)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
           <t>A | 2141呎 (4+房)
 $12168万
 $56,833/呎
-(23年-05月)</t>
+(23年-05月-14日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -12537,7 +12537,7 @@
           <t>B | 1842呎 (3房)
 $9512万
 $51,640/呎
-(23年-05月)</t>
+(23年-05月-14日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -12545,7 +12545,7 @@
           <t>C | 764呎 (2房)
 $2544万
 $33,300/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
           <t>A | 2141呎 (4+房)
 $12018万
 $56,133/呎
-(23年-04月)</t>
+(23年-04月-16日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>B | 1725呎 (3房)
 $9210万
 $53,391/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>C | 722呎 (2房)
 $2705万
 $37,465/呎
-(26年-06月)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
           <t>A | 2024呎 (4+房)
 $11900万
 $58,794/呎
-(23年-03月)</t>
+(23年-03月-29日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -12599,7 +12599,7 @@
           <t>B | 1724呎 (3房)
 $8800万
 $51,044/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -12607,7 +12607,7 @@
           <t>C | 722呎 (2房)
 $2466万
 $34,157/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
           <t>A | 2024呎 (4+房)
 $11800万
 $58,300/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -12630,7 +12630,7 @@
           <t>B | 1724呎 (3房)
 $8600万
 $49,884/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -12653,7 +12653,7 @@
           <t>A | 2140呎 (4+房)
 $11700万
 $54,673/呎
-(21年-10月)</t>
+(21年-10月-06日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12661,7 +12661,7 @@
           <t>B | 1724呎 (3房)
 $8500万
 $49,304/呎
-(25年-02月)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -12669,7 +12669,7 @@
           <t>C | 722呎 (2房)
 $2382万
 $32,992/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(20年-09月)</t>
+(20年-09月-09日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12692,7 +12692,7 @@
           <t>B | 1841呎 (3房)
 $9000万
 $48,886/呎
-(20年-12月)</t>
+(20年-12月-17日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -12700,7 +12700,7 @@
           <t>C | 722呎 (2房)
 $2340万
 $32,410/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12715,7 @@
           <t>A | 2140呎 (4+房)
 $11500万
 $53,738/呎
-(23年-01月)</t>
+(23年-01月-31日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -12723,7 +12723,7 @@
           <t>B | 1724呎 (3房)
 $8380万
 $48,608/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -12746,7 +12746,7 @@
           <t>A | 2140呎 (4+房)
 $11300万
 $52,804/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12754,7 +12754,7 @@
           <t>B | 1724呎 (3房)
 $8280万
 $48,028/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -12762,7 +12762,7 @@
           <t>C | 722呎 (2房)
 $2463万
 $34,111/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
           <t>A | 2140呎 (4+房)
 $11000万
 $51,402/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12785,7 +12785,7 @@
           <t>B | 1841呎 (3房)
 $8900万
 $48,343/呎
-(23年-01月)</t>
+(23年-01月-19日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -12793,7 +12793,7 @@
           <t>C | 722呎 (2房)
 $2510万
 $34,765/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
           <t>A | 2140呎 (4+房)
 $10500万
 $49,065/呎
-(22年-05月)</t>
+(22年-05月-30日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12816,7 +12816,7 @@
           <t>B | 1724呎 (3房)
 $8274万
 $47,993/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -12824,7 +12824,7 @@
           <t>C | 722呎 (2房)
 $2222万
 $30,776/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12839,7 @@
           <t>A | 2140呎 (4+房)
 $10280万
 $48,037/呎
-(22年-05月)</t>
+(22年-05月-18日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12847,7 +12847,7 @@
           <t>B | 1724呎 (3房)
 $7950万
 $46,114/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -12870,7 +12870,7 @@
           <t>A | 2140呎 (4+房)
 $10270万
 $47,991/呎
-(23年-01月)</t>
+(23年-01月-26日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12878,7 +12878,7 @@
           <t>B | 1724呎 (3房)
 $7838万
 $45,464/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -12886,7 +12886,7 @@
           <t>C | 722呎 (2房)
 $2178万
 $30,169/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -12901,7 +12901,7 @@
           <t>A | 2140呎 (4+房)
 $10450万
 $48,832/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12909,7 +12909,7 @@
           <t>B | 1841呎 (3房)
 $8600万
 $46,714/呎
-(23年-01月)</t>
+(23年-01月-30日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -12917,7 +12917,7 @@
           <t>C | 722呎 (2房)
 $2150万
 $29,778/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12932,7 @@
           <t>A | 2140呎 (4+房)
 $9780万
 $45,701/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12940,7 +12940,7 @@
           <t>B | 1841呎 (3房)
 $8020万
 $43,563/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -12963,7 +12963,7 @@
           <t>A | 2024呎 (4+房)
 $9680万
 $47,826/呎
-(23年-08月)</t>
+(23年-08月-28日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -12971,7 +12971,7 @@
           <t>B | 1724呎 (3房)
 $8300万
 $48,144/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -12979,7 +12979,7 @@
           <t>C | 722呎 (2房)
 $2277万
 $31,537/呎
-(26年-07月)</t>
+(26年-07月-01日)</t>
         </is>
       </c>
     </row>
@@ -12994,7 +12994,7 @@
           <t>A | 2024呎 (4+房)
 $8900万
 $43,972/呎
-(23年-12月)</t>
+(23年-12月-05日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13002,7 +13002,7 @@
           <t>B | 1724呎 (3房)
 $6900万
 $40,023/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -13010,7 +13010,7 @@
           <t>C | 722呎 (2房)
 $2254万
 $31,219/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
           <t>A | 2141呎 (4+房)
 $9300万
 $43,438/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13033,7 +13033,7 @@
           <t>B | 1725呎 (3房)
 $7030万
 $40,754/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -13056,7 +13056,7 @@
           <t>A | 2141呎 (4+房)
 $8600万
 $40,168/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13064,7 +13064,7 @@
           <t>B | 1725呎 (3房)
 $6808万
 $39,467/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13072,7 +13072,7 @@
           <t>C | 722呎 (2房)
 $2247万
 $31,122/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -13204,7 +13204,7 @@
           <t>A | 3695呎 (4+房)
 $26000万
 $70,365/呎
-(21年-06月)</t>
+(21年-06月-29日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -13228,7 +13228,7 @@
           <t>A | 1871呎 (3房)
 $9013万
 $48,172/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -13236,7 +13236,7 @@
           <t>B | 1752呎 (3房)
 $9013万
 $51,444/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -13259,7 +13259,7 @@
           <t>A | 1755呎 (3房)
 $17765万
 $101,225/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13267,7 +13267,7 @@
           <t>B | 1752呎 (3房)
 $17765万
 $101,398/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -13290,7 +13290,7 @@
           <t>A | 1755呎 (3房)
 $8690万
 $49,516/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -13298,7 +13298,7 @@
           <t>B | 1752呎 (3房)
 $8690万
 $49,600/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -13321,7 +13321,7 @@
           <t>A | 1870呎 (3房)
 $9328万
 $49,882/呎
-(21年-07月)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -13329,7 +13329,7 @@
           <t>B | 1752呎 (3房)
 $9388万
 $53,584/呎
-(23年-02月)</t>
+(23年-02月-15日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -13337,7 +13337,7 @@
           <t>C | 723呎 (2房)
 $2466万
 $34,112/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
           <t>A | 1755呎 (3房)
 $8450万
 $48,148/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -13360,7 +13360,7 @@
           <t>B | 1752呎 (3房)
 $8550万
 $48,801/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -13368,7 +13368,7 @@
           <t>C | 723呎 (2房)
 $2417万
 $33,436/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
           <t>A | 1755呎 (3房)
 $8575万
 $48,860/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -13391,7 +13391,7 @@
           <t>B | 1752呎 (3房)
 $8675万
 $49,515/呎
-(25年-07月)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -13414,7 +13414,7 @@
           <t>A | 1870呎 (3房)
 $8960万
 $47,914/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -13422,7 +13422,7 @@
           <t>B | 1868呎 (3房)
 $9060万
 $48,501/呎
-(21年-06月)</t>
+(21年-06月-01日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -13430,7 +13430,7 @@
           <t>C | 723呎 (2房)
 $2345万
 $32,430/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
           <t>A | 1755呎 (3房)
 $8149万
 $46,433/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -13453,7 +13453,7 @@
           <t>B | 1752呎 (3房)
 $8250万
 $47,089/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -13461,7 +13461,7 @@
           <t>C | 764呎 (2房)
 $2381万
 $31,170/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -13476,7 +13476,7 @@
           <t>A | 1755呎 (3房)
 $8800万
 $50,142/呎
-(25年-09月)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -13484,7 +13484,7 @@
           <t>B | 1752呎 (3房)
 $9500万
 $54,224/呎
-(24年-07月)</t>
+(24年-07月-22日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -13492,7 +13492,7 @@
           <t>C | 723呎 (2房)
 $2280万
 $31,535/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
           <t>A | 1755呎 (3房)
 $8635万
 $49,202/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -13515,7 +13515,7 @@
           <t>B | 1752呎 (3房)
 $8726万
 $49,806/呎
-(23年-02月)</t>
+(23年-02月-02日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -13523,7 +13523,7 @@
           <t>C | 723呎 (2房)
 $2258万
 $31,231/呎
-(25年-02月)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
     </row>
@@ -13538,7 +13538,7 @@
           <t>A | 1870呎 (3房)
 $8060万
 $43,102/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -13546,7 +13546,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -13569,7 +13569,7 @@
           <t>A | 1870呎 (3房)
 $8600万
 $45,989/呎
-(20年-08月)</t>
+(20年-08月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -13577,7 +13577,7 @@
           <t>B | 1868呎 (3房)
 $8638万
 $46,242/呎
-(23年-03月)</t>
+(23年-03月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -13585,7 +13585,7 @@
           <t>C | 723呎 (2房)
 $2266万
 $31,342/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
           <t>A | 1755呎 (3房)
 $8300万
 $47,293/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -13608,7 +13608,7 @@
           <t>B | 1868呎 (3房)
 $8184万
 $43,810/呎
-(23年-07月)</t>
+(23年-07月-02日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -13616,7 +13616,7 @@
           <t>C | 723呎 (2房)
 $2352万
 $32,531/呎
-(26年-06月)</t>
+(26年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -13631,7 +13631,7 @@
           <t>A | 1870呎 (3房)
 $8000万
 $42,781/呎
-(22年-05月)</t>
+(22年-05月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -13639,7 +13639,7 @@
           <t>B | 1868呎 (3房)
 $8200万
 $43,897/呎
-(23年-03月)</t>
+(23年-03月-27日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -13647,7 +13647,7 @@
           <t>C | 723呎 (2房)
 $2322万
 $32,116/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -13662,7 +13662,7 @@
           <t>A | 1755呎 (3房)
 $8808万
 $50,188/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -13670,7 +13670,7 @@
           <t>B | 1752呎 (3房)
 $8140万
 $46,461/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -13693,7 +13693,7 @@
           <t>A | 1870呎 (3房)
 $8100万
 $43,316/呎
-(23年-03月)</t>
+(23年-03月-07日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -13701,7 +13701,7 @@
           <t>B | 1752呎 (3房)
 $7580万
 $43,265/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -13709,7 +13709,7 @@
           <t>C | 723呎 (2房)
 $2185万
 $30,221/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
           <t>A | 1870呎 (3房)
 $6800万
 $36,364/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -13732,7 +13732,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -13755,7 +13755,7 @@
           <t>A | 1755呎 (3房)
 $6500万
 $37,037/呎
-(25年-05月)</t>
+(25年-05月-29日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -13763,7 +13763,7 @@
           <t>B | 1752呎 (3房)
 $6660万
 $38,014/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -13786,7 +13786,7 @@
           <t>A | 1755呎 (3房)
 $6600万
 $37,607/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -13794,7 +13794,7 @@
           <t>B | 1752呎 (3房)
 $6800万
 $38,813/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -13802,7 +13802,7 @@
           <t>C | 723呎 (2房)
 $2247万
 $31,079/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
     </row>
@@ -13934,7 +13934,7 @@
           <t>A | 3325呎 (4+房)
 $23280万
 $70,015/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -13943,7 +13943,7 @@
           <t>C | 732呎 (2房)
 $2702万
 $36,913/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -13958,7 +13958,7 @@
           <t>A | 3325呎 (4+房)
 $21800万
 $65,564/呎
-(22年-02月)</t>
+(22年-02月-09日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -13967,7 +13967,7 @@
           <t>C | 732呎 (2房)
 $2648万
 $36,174/呎
-(24年-09月)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
           <t>A | 2087呎 (4+房)
 $19300万
 $92,477/呎
-(24年-09月)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -13990,7 +13990,7 @@
           <t>B | 1840呎 (3房)
 $19300万
 $104,891/呎
-(24年-09月)</t>
+(24年-09月-19日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -13998,7 +13998,7 @@
           <t>C | 732呎 (2房)
 $2854万
 $38,989/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -14013,7 +14013,7 @@
           <t>A | 1973呎 (4+房)
 $11300万
 $57,273/呎
-(23年-05月)</t>
+(23年-05月-09日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -14021,7 +14021,7 @@
           <t>B | 1840呎 (3房)
 $8339万
 $45,322/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -14029,7 +14029,7 @@
           <t>C | 732呎 (2房)
 $2518万
 $34,399/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
           <t>A | 1972呎 (4+房)
 $9868万
 $50,041/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -14052,7 +14052,7 @@
           <t>B | 1722呎 (3房)
 $8125万
 $47,185/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -14060,7 +14060,7 @@
           <t>C | 732呎 (2房)
 $2475万
 $33,807/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
           <t>A | 1972呎 (4+房)
 $9800万
 $49,696/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -14083,7 +14083,7 @@
           <t>B | 1722呎 (3房)
 $8000万
 $46,458/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -14091,7 +14091,7 @@
           <t>C | 732呎 (2房)
 $2431万
 $33,210/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
           <t>A | 1972呎 (4+房)
 $9569万
 $48,523/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -14114,7 +14114,7 @@
           <t>B | 1722呎 (3房)
 $7850万
 $45,587/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -14122,7 +14122,7 @@
           <t>C | 732呎 (2房)
 $2395万
 $32,719/呎
-(25年-11月)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -14137,7 +14137,7 @@
           <t>A | 1972呎 (4+房)
 $9480万
 $48,073/呎
-(24年-07月)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -14145,7 +14145,7 @@
           <t>B | 1722呎 (3房)
 $7690万
 $44,657/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -14153,7 +14153,7 @@
           <t>C | 732呎 (2房)
 $2357万
 $32,199/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
           <t>A | 1972呎 (4+房)
 $9100万
 $46,146/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -14176,7 +14176,7 @@
           <t>B | 1722呎 (3房)
 $7580万
 $44,019/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -14184,7 +14184,7 @@
           <t>C | 732呎 (2房)
 $2350万
 $32,104/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
           <t>A | 2088呎 (4+房)
 $8900万
 $42,625/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -14207,7 +14207,7 @@
           <t>B | 1722呎 (3房)
 $7480万
 $43,438/呎
-(24年-07月)</t>
+(24年-07月-30日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -14215,7 +14215,7 @@
           <t>C | 732呎 (2房)
 $2315万
 $31,626/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
           <t>A | 1972呎 (4+房)
 $8850万
 $44,878/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -14238,7 +14238,7 @@
           <t>B | 1722呎 (3房)
 $7400万
 $42,973/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -14246,7 +14246,7 @@
           <t>C | 732呎 (2房)
 $2280万
 $31,148/呎
-(25年-11月)</t>
+(25年-11月-23日)</t>
         </is>
       </c>
     </row>
@@ -14261,7 +14261,7 @@
           <t>A | 1972呎 (4+房)
 $8800万
 $44,625/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -14269,7 +14269,7 @@
           <t>B | 1722呎 (3房)
 $7360万
 $42,741/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -14277,7 +14277,7 @@
           <t>C | 732呎 (2房)
 $2425万
 $33,128/呎
-(26年-06月)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
           <t>A | 1972呎 (4+房)
 $8738万
 $44,310/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -14300,7 +14300,7 @@
           <t>B | 1722呎 (3房)
 $7288万
 $42,323/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -14308,7 +14308,7 @@
           <t>C | 732呎 (2房)
 $2738万
 $37,404/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
           <t>A | 1972呎 (4+房)
 $8638万
 $43,803/呎
-(24年-08月)</t>
+(24年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -14331,7 +14331,7 @@
           <t>B | 1722呎 (3房)
 $7200万
 $41,812/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -14339,7 +14339,7 @@
           <t>C | 732呎 (2房)
 $2175万
 $29,713/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
           <t>A | 1972呎 (4+房)
 $8548万
 $43,347/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -14362,7 +14362,7 @@
           <t>B | 1722呎 (3房)
 $7000万
 $40,650/呎
-(24年-07月)</t>
+(24年-07月-16日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -14370,7 +14370,7 @@
           <t>C | 732呎 (2房)
 $2140万
 $29,235/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
           <t>A | 1972呎 (4+房)
 $8350万
 $42,343/呎
-(24年-08月)</t>
+(24年-08月-26日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -14393,7 +14393,7 @@
           <t>B | 1722呎 (3房)
 $7245万
 $42,073/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -14416,7 +14416,7 @@
           <t>A | 1972呎 (4+房)
 $8020万
 $40,669/呎
-(25年-06月)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -14424,7 +14424,7 @@
           <t>B | 1722呎 (3房)
 $6750万
 $39,199/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -14432,7 +14432,7 @@
           <t>C | 732呎 (2房)
 $2265万
 $30,943/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14447,7 @@
           <t>A | 1972呎 (4+房)
 $7780万
 $39,452/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -14455,7 +14455,7 @@
           <t>B | 1722呎 (3房)
 $6520万
 $37,863/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -14463,7 +14463,7 @@
           <t>C | 732呎 (2房)
 $2076万
 $28,361/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
           <t>A | 1973呎 (4+房)
 $7628万
 $38,662/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -14486,7 +14486,7 @@
           <t>B | 1723呎 (3房)
 $6380万
 $37,028/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -14494,7 +14494,7 @@
           <t>C | 732呎 (2房)
 $2055万
 $28,074/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
     </row>
@@ -14509,7 +14509,7 @@
           <t>A | 1973呎 (4+房)
 $7800万
 $39,534/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -14517,7 +14517,7 @@
           <t>B | 1723呎 (3房)
 $6450万
 $37,435/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -14525,7 +14525,7 @@
           <t>C | 772呎 (2房)
 $2280万
 $29,534/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
